--- a/Google_Maps_Leads.xlsx
+++ b/Google_Maps_Leads.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="عطر" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="عطر جدة" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="221">
   <si>
     <t>اسم المنشأة</t>
   </si>
@@ -119,6 +120,561 @@
   </si>
   <si>
     <t>http://ghawali.com/ar/</t>
+  </si>
+  <si>
+    <t>الرصاصي للعطور | Rasasi Perfumes | شارع التحلية - جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:6816810396490178019</t>
+  </si>
+  <si>
+    <t>Tahlia Street, Ar Rawdah, Jeddah 23432, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 59 910 7849</t>
+  </si>
+  <si>
+    <t>https://store.rasasi.com.sa/ar</t>
+  </si>
+  <si>
+    <t>لوتس للعطور LOTUS PERFUMES</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:17829528404967273688</t>
+  </si>
+  <si>
+    <t>شارع الأجواد - مقابل مستوصف السامر- بجوار عصائر الفصول الأربعة، جدة 23462, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 275 7631</t>
+  </si>
+  <si>
+    <t>http://lotusper.com/</t>
+  </si>
+  <si>
+    <t>الرحاب للعطور - ALREHAB PERFUMES - سوق المساعدية</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:11163125263016235310</t>
+  </si>
+  <si>
+    <t>Musadiyah Plaza - سوق المساعدية, Al-Madinah Al-Munawarah Rd, Al-Hamra'a, Jeddah 23324, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 9200 33928</t>
+  </si>
+  <si>
+    <t>https://www.alrehab.com/</t>
+  </si>
+  <si>
+    <t>شركة أرجوان الفخامة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:7573967544862003665</t>
+  </si>
+  <si>
+    <t>Al Warood، اوايسس مول الشرفية وحي, Jeddah 25321, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 56 184 7318</t>
+  </si>
+  <si>
+    <t>https://lenichestore.com/</t>
+  </si>
+  <si>
+    <t>إحساس ريفال للعطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:18031889343640121982</t>
+  </si>
+  <si>
+    <t>7508 Prince Mutaib bin Abdulaziz Rd, Al-Safa, Jeddah 23451, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 005 8884</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/refalperfume?igsh=MTYxNzZ3dGFxam0yNg==</t>
+  </si>
+  <si>
+    <t>ركن عالم العطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:14699438479797291954</t>
+  </si>
+  <si>
+    <t>6757 Al Makarunah Rd, Mishrifah, 4515, Jeddah 23335, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 55 336 3563</t>
+  </si>
+  <si>
+    <t>(الشرقية الماسية)zamani perfumes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:2787261244625345745</t>
+  </si>
+  <si>
+    <t>JACC6512, 3175 Al Dhahab, 6512، Jeddah 22233, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 54 224 4949</t>
+  </si>
+  <si>
+    <t>http://zamaniperfumes.com/</t>
+  </si>
+  <si>
+    <t>محل الماركات العالمية للعطورات</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:9694522421548411426</t>
+  </si>
+  <si>
+    <t>Baishin, Al-Balad, Jeddah 22233, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 322 9117</t>
+  </si>
+  <si>
+    <t>عطور فيصل الدايل</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:527312276479999303</t>
+  </si>
+  <si>
+    <t>Prince Mohammed Bin Abdulaziz St, Ar Rawdah, Jeddah 23432, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 9200 22540</t>
+  </si>
+  <si>
+    <t>https://faisalaldayel.com/</t>
+  </si>
+  <si>
+    <t>Al-Andalus Perfumes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:11353005053395304055</t>
+  </si>
+  <si>
+    <t>Suq Bab Makkah, Historic Jeddah, Jeddah 22236, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 50 757 4840</t>
+  </si>
+  <si>
+    <t>Aromatic</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:12659332265285695118</t>
+  </si>
+  <si>
+    <t>King Fahad Rd, Aziziyah, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 9203 11561</t>
+  </si>
+  <si>
+    <t>https://aromatic.sa/</t>
+  </si>
+  <si>
+    <t>Bloom - جدة بارك</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:9954467324170560261</t>
+  </si>
+  <si>
+    <t>Aziziyah، 9060 طريق الملك فهد، حي العزيزية، جدة 23334 3286, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>الرصاصي للعطور | Rasasi Perfumes | البلد - جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:13449787184181601389</t>
+  </si>
+  <si>
+    <t>F5JP+8MQ, Salah Ad Din, Historic Jeddah, Jeddah 22233, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Almusbah perfumes عطور المصباح البلد</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:2741745172789753629</t>
+  </si>
+  <si>
+    <t>الملك عبدالعزيز, Historic Jeddah, Jeddah 22233, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 55 062 4550</t>
+  </si>
+  <si>
+    <t>ديلينا للعطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:4380539820239773058</t>
+  </si>
+  <si>
+    <t>طريق، المدينة - المساعدية سوق المساعدية, Jeddah 23324, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 50 365 1335</t>
+  </si>
+  <si>
+    <t>https://delina1.com/</t>
+  </si>
+  <si>
+    <t>ركن باريس للعطور ومستحضرات التجميل</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:9927947709656281150</t>
+  </si>
+  <si>
+    <t>مركز الكورنيش التجاري بوابة 9 - الدور الخامس معرض ركن باريس، شارع الملك عبدالعزيز, Historic Jeddah, Jeddah 22233, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 55 446 9687</t>
+  </si>
+  <si>
+    <t>https://paris-corner.com/</t>
+  </si>
+  <si>
+    <t>البيت الإماراتي للعودEmirates Bait perfume shop</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:11911599747605377551</t>
+  </si>
+  <si>
+    <t>+966 9200 01438</t>
+  </si>
+  <si>
+    <t>https://emiratisbait.com/</t>
+  </si>
+  <si>
+    <t>قصة للعطور | Gissah Perfumes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:504364218669550166</t>
+  </si>
+  <si>
+    <t>Al Faisaliyyah, Jeddah 23447, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 11 511 9700</t>
+  </si>
+  <si>
+    <t>https://www.gissah.com/</t>
+  </si>
+  <si>
+    <t>Shurfan Perfumes شرفان بانافع</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:8535389856748306911</t>
+  </si>
+  <si>
+    <t>سوق المساعدية ،, Jeddah 23324, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 55 088 5166</t>
+  </si>
+  <si>
+    <t>https://shurfan.net/</t>
+  </si>
+  <si>
+    <t>سعيد صلاح للعطور و التجميل</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:1644897718591087293</t>
+  </si>
+  <si>
+    <t>الدور الخامس, حي الورود - طريق الملك عبدالله أويسيس مول, Jeddah 00244, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 50 098 7753</t>
+  </si>
+  <si>
+    <t>https://saeedsalah.com/</t>
+  </si>
+  <si>
+    <t>مصنع الثمين لصناعة العطور فرع جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:7482129290048832243</t>
+  </si>
+  <si>
+    <t>برج البلاتيني مصنع الثمين, Al Faisaliyyah, Jeddah 23442, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 029 4449</t>
+  </si>
+  <si>
+    <t>https://linktr.ee/althameen1</t>
+  </si>
+  <si>
+    <t>Perfume Makers Experts</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:9936254949928426697</t>
+  </si>
+  <si>
+    <t>King Fahad Rd, Al Sharafeyah, Jeddah 23216, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 12 614 0002</t>
+  </si>
+  <si>
+    <t>بوتيك ثروة للعطور فرع جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:14290208250516501689</t>
+  </si>
+  <si>
+    <t>8683 2623 Abdul Maqsud Khojah, Ar Rawdah, Jeddah 23435, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>https://tharwahperfume.com/</t>
+  </si>
+  <si>
+    <t>عطر خاص</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:10466307064330741988</t>
+  </si>
+  <si>
+    <t>Prince Majid Rd, Al Faisaliyyah, Jeddah 22230, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 59 099 6126</t>
+  </si>
+  <si>
+    <t>Dkhoun | دخون</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:7105970042152140355</t>
+  </si>
+  <si>
+    <t>Prince Sultan Rd, Al Zahra, Jeddah 23425, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 11 244 0224</t>
+  </si>
+  <si>
+    <t>http://www.dkhoun.com/</t>
+  </si>
+  <si>
+    <t>دكنه للعطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:2874123299058055085</t>
+  </si>
+  <si>
+    <t>Prince Mohammed Bin Abdulaziz St, Aziziyah, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 59 555 4469</t>
+  </si>
+  <si>
+    <t>http://www.doknah.com.sa/</t>
+  </si>
+  <si>
+    <t>عطور بازل</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:13380405975581242157</t>
+  </si>
+  <si>
+    <t>8005 4722 Ahmad Al Mouftah, Al-Safa, Jeddah 23454, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 964 4776</t>
+  </si>
+  <si>
+    <t>Junaid Perfumes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:1457777247173111789</t>
+  </si>
+  <si>
+    <t>Souq al Murjan Abdul ground floor، Abdul Aziz Ibn Ibrahim, Al-Safa, Jeddah 23454, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 11 486 9141</t>
+  </si>
+  <si>
+    <t>https://www.junaidperfumes.com/</t>
+  </si>
+  <si>
+    <t>عطور جمله</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:17467673486569112354</t>
+  </si>
+  <si>
+    <t>Suq Bab Makkah, Historic Jeddah, Jeddah 21442, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 56 167 1237</t>
+  </si>
+  <si>
+    <t>The Scent Box ذا سنت بوكس</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:6581211740698548114</t>
+  </si>
+  <si>
+    <t>Darwish Kayyal, Ar Rawdah, Jeddah 23433, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 50 650 6662</t>
+  </si>
+  <si>
+    <t>http://www.thescentboxksa.com/</t>
+  </si>
+  <si>
+    <t>ريف - Reef</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:14480919266667661172</t>
+  </si>
+  <si>
+    <t>Palestine, Al-Ruwais, هيفاء مول, Jeddah 23215, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 9200 12246</t>
+  </si>
+  <si>
+    <t>https://reefperfumes.com/</t>
+  </si>
+  <si>
+    <t>الرصاصي للعطور | Rasasi Perfumes | الأندلس مول - جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:9152522360544167745</t>
+  </si>
+  <si>
+    <t>Prince Majid Rd، بوابة 2،3، الاندلس مول, Jeddah 22245, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>AJMAL</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:4724889144743394482</t>
+  </si>
+  <si>
+    <t>الأندلس مول, Prince Majid Rd، طريق المطار القديم, Jeddah Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 50 551 6533</t>
+  </si>
+  <si>
+    <t>https://ar-sa.ajmal.com/</t>
+  </si>
+  <si>
+    <t>أماسي للعطور جمله وتجزائه</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:12593375049056147835</t>
+  </si>
+  <si>
+    <t>3402 زقاق الصوري, Al Balad District، حي البلد،, Jeddah 22236, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 6426028</t>
+  </si>
+  <si>
+    <t>Ajmal Perfumes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:3394546838399228618</t>
+  </si>
+  <si>
+    <t>Prince Mohammed Bin Abdulaziz Branch Rd, Ar Rawdah, Jeddah 23432, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 055 8839</t>
+  </si>
+  <si>
+    <t>الرصاصي للعطور | Rasasi Perfumes | جدة بارك - جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:5792206718387777314</t>
+  </si>
+  <si>
+    <t>بارك, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>DERAAH</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:3881337088180326176</t>
+  </si>
+  <si>
+    <t>H54M+Ccc، 3039 Prince Mohammed Bin Abdulaziz St، حي العزيزية، 8951 العزيزية، جدة SA, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 800 118 6666</t>
+  </si>
+  <si>
+    <t>https://www.deraahstore.com/</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:15259825376258540539</t>
+  </si>
+  <si>
+    <t>Al Faisaliyyah, Aziz Mall, Gate 2, Jeddah 23447, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 53 920 0851</t>
+  </si>
+  <si>
+    <t>نارسيس | narcisse</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:13817958771175688537</t>
+  </si>
+  <si>
+    <t>بارك مول - الدور الاول مقابل الرصاصي, Prince Mohammed Bin Abdulaziz St, Jeddah park mall, 1st floor, Jeddah 23334, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>+966 59 035 8542</t>
+  </si>
+  <si>
+    <t>https://narcisseksa.com/</t>
+  </si>
+  <si>
+    <t>Surrati Perfumes | السرتي للعطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:5152637600738755210</t>
+  </si>
+  <si>
+    <t>6377 محمد بن عبدالعزيز، AR Rawdah District, 3620 Al Amir, Jeddah 23432, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>https://surrati.sa/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAb21jcAQ-H6xleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafDDeuzWUJvfdMjZQCUpU_uoLGDmHZ29vK0ceotlPPVZQEynUd3RNe_K1mjdg_aem_E8FO8-jTAnDr9upcl_v2HA</t>
+  </si>
+  <si>
+    <t>بيت العطور</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:3039819549920252676</t>
+  </si>
+  <si>
+    <t>Prince Majid Rd، الاندلس مول, Jeddah 22245, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>الرصاصي للعطور | Rasasi Perfumes | عزيز مول - جدة</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:3997368014425493368</t>
+  </si>
+  <si>
+    <t>Prince Majid Rd, Al Faisaliyyah, Jeddah 23447, Saudi Arabia</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/?q=place_id:12025564551338186157</t>
+  </si>
+  <si>
+    <t>Ar Rawdah, Jeddah 23434, Saudi Arabia</t>
   </si>
 </sst>
 </file>
@@ -685,6 +1241,1304 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+      <c r="D2">
+        <v>391</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3">
+        <v>4.8</v>
+      </c>
+      <c r="D3">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>4.9</v>
+      </c>
+      <c r="D4">
+        <v>334</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5">
+        <v>4.9</v>
+      </c>
+      <c r="D5">
+        <v>2229</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6">
+        <v>4.7</v>
+      </c>
+      <c r="D6">
+        <v>203</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>4.7</v>
+      </c>
+      <c r="D7">
+        <v>131</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9">
+        <v>4.8</v>
+      </c>
+      <c r="D9">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10">
+        <v>4.3</v>
+      </c>
+      <c r="D10">
+        <v>838</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>4.7</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>416</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13">
+        <v>4.3</v>
+      </c>
+      <c r="D13">
+        <v>137</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14">
+        <v>4.1</v>
+      </c>
+      <c r="D14">
+        <v>259</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15">
+        <v>4.3</v>
+      </c>
+      <c r="D15">
+        <v>161</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>284</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>4.7</v>
+      </c>
+      <c r="D17">
+        <v>193</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18">
+        <v>4.3</v>
+      </c>
+      <c r="D18">
+        <v>494</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19">
+        <v>4.3</v>
+      </c>
+      <c r="D19">
+        <v>39</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20">
+        <v>4.6</v>
+      </c>
+      <c r="D20">
+        <v>148</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21">
+        <v>4.9</v>
+      </c>
+      <c r="D21">
+        <v>193</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23">
+        <v>4.1</v>
+      </c>
+      <c r="D23">
+        <v>161</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24">
+        <v>4.7</v>
+      </c>
+      <c r="D24">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>139</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25">
+        <v>4.5</v>
+      </c>
+      <c r="D25">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>142</v>
+      </c>
+      <c r="G25" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26">
+        <v>4.7</v>
+      </c>
+      <c r="D26">
+        <v>179</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27">
+        <v>4.7</v>
+      </c>
+      <c r="D27">
+        <v>116</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28">
+        <v>4.7</v>
+      </c>
+      <c r="D28">
+        <v>155</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>156</v>
+      </c>
+      <c r="G28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29">
+        <v>4.6</v>
+      </c>
+      <c r="D29">
+        <v>81</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>165</v>
+      </c>
+      <c r="G30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31">
+        <v>4.9</v>
+      </c>
+      <c r="D31">
+        <v>163</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" t="s">
+        <v>170</v>
+      </c>
+      <c r="H31" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32">
+        <v>4.1</v>
+      </c>
+      <c r="D32">
+        <v>53</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33">
+        <v>4.8</v>
+      </c>
+      <c r="D33">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34">
+        <v>4.2</v>
+      </c>
+      <c r="D34">
+        <v>336</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35">
+        <v>4.4</v>
+      </c>
+      <c r="D35">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36">
+        <v>4.3</v>
+      </c>
+      <c r="D36">
+        <v>375</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>191</v>
+      </c>
+      <c r="G36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" t="s">
+        <v>184</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37">
+        <v>4.1</v>
+      </c>
+      <c r="D37">
+        <v>47</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
+        <v>195</v>
+      </c>
+      <c r="G37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>197</v>
+      </c>
+      <c r="C38">
+        <v>4.5</v>
+      </c>
+      <c r="D38">
+        <v>95</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" t="s">
+        <v>200</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
+        <v>202</v>
+      </c>
+      <c r="G39" t="s">
+        <v>203</v>
+      </c>
+      <c r="H39" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40">
+        <v>4.4</v>
+      </c>
+      <c r="D40">
+        <v>54</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>206</v>
+      </c>
+      <c r="G40" t="s">
+        <v>207</v>
+      </c>
+      <c r="H40" t="s">
+        <v>208</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41">
+        <v>4.1</v>
+      </c>
+      <c r="D41">
+        <v>57</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>211</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
+        <v>212</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42">
+        <v>4.7</v>
+      </c>
+      <c r="D42">
+        <v>30</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>215</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43">
+        <v>4.5</v>
+      </c>
+      <c r="D43">
+        <v>147</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" t="s">
+        <v>40</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44">
+        <v>4.7</v>
+      </c>
+      <c r="D44">
+        <v>150</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>220</v>
+      </c>
+      <c r="G44" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>